--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-reference-item-plan-traitement.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-reference-item-plan-traitement.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$141</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4364" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4396" uniqueCount="414">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -938,6 +938,22 @@
   </si>
   <si>
     <t>Material.lotNumberText</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturedMaterial.sdtcExpirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>The date and time the manufacturer no longer ensures the safety, quality, and/or proper functioning of the material.</t>
+  </si>
+  <si>
+    <t>There is a need in many situations that the materials used are of a specific quality or potency or functional status. The ending date for this guarantee is specified by the manufacturer. After that date, while the material may still provide the same characteristics, the manufacturer no longer takes responsibility that the product will perform as specified and denies responsibility for failure of the material after that date.</t>
+  </si>
+  <si>
+    <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
     <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturerOrganization</t>
@@ -1610,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK140"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.61328125" customWidth="true" bestFit="true"/>
@@ -1627,7 +1643,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -10782,9 +10798,13 @@
         <v>300</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
+      <c r="M91" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>74</v>
       </c>
@@ -10832,7 +10852,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10852,10 +10872,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10878,7 +10898,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10931,7 +10951,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10951,10 +10971,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10965,7 +10985,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -10977,7 +10997,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11030,13 +11050,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -11050,10 +11070,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11076,7 +11096,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11129,7 +11149,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11149,10 +11169,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11160,10 +11180,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11175,14 +11195,10 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11232,7 +11248,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11252,10 +11268,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11263,10 +11279,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11278,10 +11294,14 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11331,7 +11351,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11351,10 +11371,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11377,7 +11397,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11430,7 +11450,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11448,12 +11468,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11461,13 +11481,13 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>74</v>
@@ -11476,14 +11496,10 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11533,7 +11549,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11551,28 +11567,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>74</v>
@@ -11581,11 +11595,13 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L99" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="M99" t="s" s="2">
-        <v>86</v>
+        <v>323</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11612,11 +11628,13 @@
         <v>74</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11634,13 +11652,13 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>89</v>
+        <v>320</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
@@ -11654,21 +11672,23 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>74</v>
@@ -11680,11 +11700,11 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11711,13 +11731,11 @@
         <v>74</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>74</v>
@@ -11735,13 +11753,13 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>74</v>
@@ -11755,10 +11773,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11769,7 +11787,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
@@ -11781,11 +11799,11 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11836,19 +11854,19 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>74</v>
@@ -11856,18 +11874,16 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
@@ -11884,11 +11900,11 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11915,11 +11931,13 @@
         <v>74</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>74</v>
@@ -11937,7 +11955,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11949,7 +11967,7 @@
         <v>74</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>74</v>
@@ -11957,17 +11975,17 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>80</v>
@@ -11985,11 +12003,11 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12016,13 +12034,11 @@
         <v>74</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -12040,7 +12056,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12060,17 +12076,17 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>80</v>
@@ -12088,11 +12104,11 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12143,7 +12159,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12163,20 +12179,20 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>75</v>
@@ -12191,11 +12207,11 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12204,7 +12220,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>74</v>
@@ -12246,7 +12262,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12266,17 +12282,17 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>75</v>
@@ -12294,11 +12310,11 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12307,7 +12323,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>74</v>
@@ -12349,7 +12365,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12369,21 +12385,23 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>74</v>
@@ -12395,11 +12413,11 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12450,13 +12468,13 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>74</v>
@@ -12470,10 +12488,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12481,10 +12499,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12496,10 +12514,12 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
+      <c r="M108" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12510,7 +12530,7 @@
         <v>74</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>329</v>
+        <v>74</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>74</v>
@@ -12525,11 +12545,13 @@
         <v>74</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>330</v>
+        <v>74</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12547,13 +12569,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>331</v>
+        <v>125</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12567,10 +12589,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12578,7 +12600,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>75</v>
@@ -12593,12 +12615,10 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" t="s" s="2">
-        <v>333</v>
-      </c>
+      <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12609,7 +12629,7 @@
         <v>74</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>74</v>
@@ -12624,13 +12644,11 @@
         <v>74</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>74</v>
+        <v>335</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12648,10 +12666,10 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>75</v>
@@ -12668,10 +12686,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12698,12 +12716,12 @@
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
-        <v>337</v>
+        <v>74</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
@@ -12749,7 +12767,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12769,10 +12787,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12798,11 +12816,13 @@
         <v>107</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
+      <c r="M111" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
@@ -12848,7 +12868,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12868,10 +12888,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12894,7 +12914,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12947,7 +12967,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12967,10 +12987,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12993,7 +13013,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13046,7 +13066,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13066,10 +13086,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13092,7 +13112,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13145,7 +13165,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13165,10 +13185,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13191,7 +13211,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13244,7 +13264,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13264,10 +13284,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13290,7 +13310,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13343,7 +13363,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13363,10 +13383,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13389,7 +13409,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13442,7 +13462,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13462,10 +13482,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13488,7 +13508,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13541,7 +13561,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13561,10 +13581,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13587,7 +13607,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13640,7 +13660,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13660,10 +13680,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13686,7 +13706,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13739,7 +13759,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13759,10 +13779,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13785,7 +13805,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -13838,7 +13858,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13858,10 +13878,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13884,7 +13904,7 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -13937,7 +13957,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -13955,12 +13975,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13974,7 +13994,7 @@
         <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>74</v>
@@ -13983,14 +14003,10 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M123" t="s" s="2">
         <v>377</v>
       </c>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14040,13 +14056,13 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>74</v>
@@ -14058,20 +14074,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E124" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
@@ -14079,7 +14093,7 @@
         <v>75</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>74</v>
@@ -14088,11 +14102,13 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L124" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="M124" t="s" s="2">
-        <v>86</v>
+        <v>382</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14119,11 +14135,13 @@
         <v>74</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y124" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z124" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>74</v>
@@ -14141,13 +14159,13 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>89</v>
+        <v>379</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>74</v>
@@ -14161,21 +14179,23 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>74</v>
@@ -14187,11 +14207,11 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14218,13 +14238,11 @@
         <v>74</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14242,13 +14260,13 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>74</v>
@@ -14262,10 +14280,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14276,7 +14294,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>74</v>
@@ -14288,11 +14306,11 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14343,19 +14361,19 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>74</v>
@@ -14363,18 +14381,16 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E127" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
@@ -14391,11 +14407,11 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14422,11 +14438,13 @@
         <v>74</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y127" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z127" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>74</v>
@@ -14444,7 +14462,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14456,7 +14474,7 @@
         <v>74</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>74</v>
@@ -14464,17 +14482,17 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>80</v>
@@ -14492,11 +14510,11 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14523,13 +14541,11 @@
         <v>74</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>74</v>
@@ -14547,7 +14563,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14567,17 +14583,17 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F129" t="s" s="2">
         <v>80</v>
@@ -14595,11 +14611,11 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14650,7 +14666,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14670,20 +14686,20 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F130" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>75</v>
@@ -14698,11 +14714,11 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14711,7 +14727,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>74</v>
@@ -14753,7 +14769,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14773,17 +14789,17 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>75</v>
@@ -14801,11 +14817,11 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -14814,7 +14830,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>74</v>
@@ -14856,7 +14872,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14876,21 +14892,23 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E132" s="2"/>
+      <c r="E132" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F132" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>74</v>
@@ -14902,11 +14920,11 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -14957,13 +14975,13 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>74</v>
@@ -14977,10 +14995,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -14988,10 +15006,10 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>74</v>
@@ -15003,10 +15021,12 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
+      <c r="M133" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -15017,7 +15037,7 @@
         <v>74</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>388</v>
+        <v>74</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>74</v>
@@ -15032,11 +15052,13 @@
         <v>74</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y133" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z133" t="s" s="2">
-        <v>389</v>
+        <v>74</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>74</v>
@@ -15054,13 +15076,13 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>390</v>
+        <v>125</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>74</v>
@@ -15074,10 +15096,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15085,7 +15107,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>75</v>
@@ -15100,7 +15122,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>345</v>
+        <v>85</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15114,7 +15136,7 @@
         <v>74</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>74</v>
+        <v>393</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>74</v>
@@ -15129,13 +15151,11 @@
         <v>74</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>74</v>
+        <v>394</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>74</v>
@@ -15153,10 +15173,10 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>75</v>
@@ -15173,10 +15193,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15199,7 +15219,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15252,7 +15272,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15272,10 +15292,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15298,7 +15318,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15351,7 +15371,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15371,10 +15391,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15397,7 +15417,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15450,7 +15470,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15468,12 +15488,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15481,13 +15501,13 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>74</v>
@@ -15496,7 +15516,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15549,7 +15569,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15567,12 +15587,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15580,13 +15600,13 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>74</v>
@@ -15595,7 +15615,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15648,13 +15668,13 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>74</v>
@@ -15668,10 +15688,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15694,7 +15714,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -15747,7 +15767,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15765,8 +15785,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK140">
+  <autoFilter ref="A1:AK141">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15776,7 +15895,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI139">
+  <conditionalFormatting sqref="A2:AI140">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
